--- a/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-s02-mapa-pontuacao-individual-v01.xlsx
+++ b/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-s02-mapa-pontuacao-individual-v01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCF419F-787D-4318-8B09-C392A2B7CFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{9CCF419F-787D-4318-8B09-C392A2B7CFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01E38B2-6A29-416C-9362-B0E343E29533}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa de Pontuação Individual" sheetId="1" r:id="rId1"/>
@@ -887,9 +887,6 @@
     <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.xlsx</t>
   </si>
   <si>
-    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.pdf</t>
-  </si>
-  <si>
     <t>I011</t>
   </si>
   <si>
@@ -984,6 +981,9 @@
   </si>
   <si>
     <t>André Filipe Moreira Mesquita; Gonçalo Dinis Magalhães Teixeira; Gonçalo Magalhães Ribeiro</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-20261007-sprint-backlog-v01.pdf</t>
   </si>
 </sst>
 </file>
@@ -1375,48 +1375,6 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1435,59 +1393,53 @@
     <xf numFmtId="164" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB4C6E7"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFB4C6E7"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFB4C6E7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB4C6E7"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFB4C6E7"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFB4C6E7"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB4C6E7"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFB4C6E7"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFB4C6E7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB4C6E7"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFB4C6E7"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFB4C6E7"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <b/>
@@ -1539,15 +1491,25 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4C6E7"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFB4C6E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4C6E7"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFB4C6E7"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFB4C6E7"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1601,7 +1563,33 @@
         <left style="thin">
           <color rgb="FFB4C6E7"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFB4C6E7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4C6E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4C6E7"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFB4C6E7"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFB4C6E7"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4C6E7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4C6E7"/>
+        </right>
         <top style="thin">
           <color rgb="FFB4C6E7"/>
         </top>
@@ -1778,6 +1766,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2300,50 +2289,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DetalhePontuacaoTable" displayName="DetalhePontuacaoTable" ref="A17:Z57" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DetalhePontuacaoTable" displayName="DetalhePontuacaoTable" ref="A17:Z57" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Sprint" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Issue" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tarefa" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aluno" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Papel" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Orçamento da tarefa" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Origem da parcela" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="PMI" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Referência da transferência" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="PC" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="PR" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="PMR" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Sprint" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Issue" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tarefa" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aluno" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Papel" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Orçamento da tarefa" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Origem da parcela" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="PMI" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Referência da transferência" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="PC" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="PR" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="PMR" dataDxfId="19">
       <calculatedColumnFormula>IF($A18="","",$H18-$J18+$K18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Categoria de qualidade aprovada" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Q" dataDxfId="1">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Categoria de qualidade aprovada" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Q" dataDxfId="17">
       <calculatedColumnFormula>IF($A18="","",IF($M18="","",IF($E18="Executor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E18="Revisor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E18="Auditor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E18="Secretário",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Fundamento e evidência" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Classificação atribuída por" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="PQ" dataDxfId="18">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Fundamento e evidência" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Classificação atribuída por" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="PQ" dataDxfId="14">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($L18)),NOT(ISNUMBER($N18))),"",$L18*$N18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Prazo aplicável" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Data e hora de conclusão" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Atraso imputável em horas" dataDxfId="15">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Prazo aplicável" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Data e hora de conclusão" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Atraso imputável em horas" dataDxfId="11">
       <calculatedColumnFormula>IF(OR($A18="",$R18="",$S18=""),"",MAX(0,($S18-$R18)*24))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Penalização por atraso" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="A" dataDxfId="0">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Penalização por atraso" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="A" dataDxfId="9">
       <calculatedColumnFormula>IF($A18="","",IF($U18="","",IFERROR(VLOOKUP($U18,'[1]Listas de apoio'!$S$5:$T$10,2,FALSE),"")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="Perda por qualidade" dataDxfId="13">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="Perda por qualidade" dataDxfId="8">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($L18)),NOT(ISNUMBER($Q18))),"",$L18-$Q18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="PEO não arredondado" dataDxfId="12">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="PEO não arredondado" dataDxfId="7">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($Q18)),NOT(ISNUMBER($V18))),"",$Q18*(1-$V18))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="Perda por atraso" dataDxfId="11">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="Perda por atraso" dataDxfId="6">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($Q18)),NOT(ISNUMBER($X18))),"",$Q18-$X18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0100-00001A000000}" name="PEO" dataDxfId="10">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0100-00001A000000}" name="PEO" dataDxfId="5">
       <calculatedColumnFormula>IF(NOT(ISNUMBER($X18)),"",ROUND($X18,2))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2550,66 +2539,66 @@
     <tabColor rgb="FF17365D"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.3984375" customWidth="1"/>
-    <col min="4" max="4" width="22.59765625" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.375" customWidth="1"/>
+    <col min="4" max="4" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="34" t="s">
+      <c r="A1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.1" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2623,29 +2612,29 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="50" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2678,7 +2667,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="29"/>
     </row>
-    <row r="7" spans="1:9" ht="25.2" customHeight="1">
+    <row r="7" spans="1:9" ht="25.15" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
@@ -2707,7 +2696,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="28.2" customHeight="1">
+    <row r="9" spans="1:9" ht="28.15" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
@@ -2722,7 +2711,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="26.4" customHeight="1">
+    <row r="10" spans="1:9" ht="26.45" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
@@ -2747,33 +2736,33 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="21.9" customHeight="1">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:9" ht="21.95" customHeight="1">
+      <c r="A12" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="50" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="33.9" customHeight="1">
+    <row r="13" spans="1:9" ht="33.950000000000003" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2833,7 +2822,7 @@
         <v>19.522546419098148</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" ht="24">
       <c r="A15" s="7" t="str">
         <f>'Listas de apoio'!A6</f>
         <v>Gonçalo Dinis Magalhães Teixeira</v>
@@ -2972,29 +2961,29 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="21.9" customHeight="1">
-      <c r="A20" s="31" t="s">
+    <row r="20" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A20" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="H20" s="50" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3048,7 +3037,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="22.8">
+    <row r="24" spans="1:8" ht="24">
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
@@ -3076,22 +3065,22 @@
       <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="50" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="1"/>
@@ -3374,7 +3363,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="24">
       <c r="A37" s="10" t="s">
         <v>33</v>
       </c>
@@ -3456,11 +3445,11 @@
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
   <dimension ref="A1:AF62"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="32.796875" customWidth="1"/>
-    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="3" max="3" width="32.75" customWidth="1"/>
+    <col min="4" max="4" width="26.125" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
@@ -3484,162 +3473,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="26.1" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="34" t="s">
+      <c r="V1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="34" t="s">
+      <c r="W1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="X1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="34" t="s">
+      <c r="Y1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="34" t="s">
+      <c r="Z1" s="37" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="44.1" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="Q2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="36" t="s">
+      <c r="R2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="36" t="s">
+      <c r="S2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="36" t="s">
+      <c r="T2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="36" t="s">
+      <c r="U2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="36" t="s">
+      <c r="W2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="X2" s="36" t="s">
+      <c r="X2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="36" t="s">
+      <c r="Y2" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="40" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3671,14 +3660,14 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:32" ht="21.9" customHeight="1">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:32" ht="21.95" customHeight="1">
+      <c r="A4" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="43" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="1"/>
@@ -3705,39 +3694,39 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="33.9" customHeight="1">
+    <row r="5" spans="1:32" s="11" customFormat="1" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="39"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3749,35 +3738,35 @@
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="44" t="s">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="46" t="s">
         <v>265</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -3789,35 +3778,35 @@
       <c r="A7" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="46" t="s">
         <v>269</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -3827,31 +3816,31 @@
     </row>
     <row r="8" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="47"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="47"/>
+      <c r="V8" s="47"/>
+      <c r="W8" s="47"/>
+      <c r="X8" s="47"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -3861,31 +3850,31 @@
     </row>
     <row r="9" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="47"/>
+      <c r="X9" s="47"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -3895,31 +3884,31 @@
     </row>
     <row r="10" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+      <c r="W10" s="47"/>
+      <c r="X10" s="47"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -3929,31 +3918,31 @@
     </row>
     <row r="11" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
@@ -3963,31 +3952,31 @@
     </row>
     <row r="12" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="47"/>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -3997,31 +3986,31 @@
     </row>
     <row r="13" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A13" s="3"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="47"/>
+      <c r="X13" s="47"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -4031,31 +4020,31 @@
     </row>
     <row r="14" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="47"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="47"/>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -4091,83 +4080,83 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:32" ht="21.9" customHeight="1">
-      <c r="A16" s="43" t="s">
+    <row r="16" spans="1:32" ht="21.95" customHeight="1">
+      <c r="A16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="43" t="s">
+      <c r="G16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="43" t="s">
+      <c r="H16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="43" t="s">
+      <c r="I16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="43" t="s">
+      <c r="J16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="43" t="s">
+      <c r="K16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="43" t="s">
+      <c r="L16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="M16" s="43" t="s">
+      <c r="M16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="43" t="s">
+      <c r="N16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="43" t="s">
+      <c r="O16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="P16" s="43" t="s">
+      <c r="P16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="Q16" s="43" t="s">
+      <c r="Q16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="R16" s="43" t="s">
+      <c r="R16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="S16" s="43" t="s">
+      <c r="S16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="T16" s="43" t="s">
+      <c r="T16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="U16" s="43" t="s">
+      <c r="U16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="43" t="s">
+      <c r="V16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="W16" s="43" t="s">
+      <c r="W16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="X16" s="43" t="s">
+      <c r="X16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="Y16" s="43" t="s">
+      <c r="Y16" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="Z16" s="43" t="s">
+      <c r="Z16" s="44" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4256,10 +4245,10 @@
         <v>267</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>259</v>
@@ -4346,10 +4335,10 @@
         <v>267</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>258</v>
@@ -4436,10 +4425,10 @@
         <v>267</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>257</v>
@@ -4526,10 +4515,10 @@
         <v>267</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>257</v>
@@ -4616,10 +4605,10 @@
         <v>267</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>259</v>
@@ -4706,10 +4695,10 @@
         <v>267</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>256</v>
@@ -4751,7 +4740,7 @@
         <v>73</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q23" s="13">
         <f t="shared" si="1"/>
@@ -4796,10 +4785,10 @@
         <v>267</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>256</v>
@@ -4886,10 +4875,10 @@
         <v>267</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>257</v>
@@ -4976,10 +4965,10 @@
         <v>267</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>259</v>
@@ -5021,7 +5010,7 @@
         <v>73</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q26" s="13">
         <f t="shared" si="1"/>
@@ -5066,10 +5055,10 @@
         <v>267</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>257</v>
@@ -5156,10 +5145,10 @@
         <v>267</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>259</v>
@@ -5246,10 +5235,10 @@
         <v>267</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>258</v>
@@ -5291,7 +5280,7 @@
         <v>73</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q29" s="13">
         <f t="shared" si="1"/>
@@ -5336,10 +5325,10 @@
         <v>267</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>258</v>
@@ -5426,10 +5415,10 @@
         <v>267</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>256</v>
@@ -5516,10 +5505,10 @@
         <v>267</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>259</v>
@@ -5561,7 +5550,7 @@
         <v>73</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q32" s="13">
         <f t="shared" si="1"/>
@@ -5606,10 +5595,10 @@
         <v>267</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>289</v>
+        <v>275</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>288</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>259</v>
@@ -5696,10 +5685,10 @@
         <v>267</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C34" s="45" t="s">
-        <v>289</v>
+        <v>275</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>288</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>257</v>
@@ -5786,13 +5775,13 @@
         <v>267</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>289</v>
+        <v>275</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>288</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>71</v>
@@ -5831,7 +5820,7 @@
         <v>73</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q35" s="13">
         <f t="shared" si="1"/>
@@ -5876,10 +5865,10 @@
         <v>267</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>257</v>
@@ -5966,10 +5955,10 @@
         <v>267</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>259</v>
@@ -6056,10 +6045,10 @@
         <v>267</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>258</v>
@@ -6101,7 +6090,7 @@
         <v>73</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q38" s="13">
         <f t="shared" si="1"/>
@@ -6146,10 +6135,10 @@
         <v>267</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>256</v>
@@ -6236,10 +6225,10 @@
         <v>267</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>258</v>
@@ -6326,10 +6315,10 @@
         <v>267</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>259</v>
@@ -6371,7 +6360,7 @@
         <v>73</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q41" s="13">
         <f t="shared" si="1"/>
@@ -6416,10 +6405,10 @@
         <v>267</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>257</v>
@@ -6506,10 +6495,10 @@
         <v>267</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>259</v>
@@ -6596,10 +6585,10 @@
         <v>267</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>256</v>
@@ -6641,7 +6630,7 @@
         <v>73</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q44" s="13">
         <f t="shared" si="1"/>
@@ -6686,10 +6675,10 @@
         <v>267</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>256</v>
@@ -6727,7 +6716,7 @@
         <f>IF($A45="","",IF($M45="","",IF($E45="Executor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E45="Revisor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E45="Auditor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E45="Secretário",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O45" s="46" t="s">
+      <c r="O45" s="32" t="s">
         <v>261</v>
       </c>
       <c r="P45" s="20" t="s">
@@ -6776,10 +6765,10 @@
         <v>267</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>258</v>
@@ -6866,10 +6855,10 @@
         <v>267</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>257</v>
@@ -6956,10 +6945,10 @@
         <v>267</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>257</v>
@@ -6997,7 +6986,7 @@
         <f>IF($A48="","",IF($M48="","",IF($E48="Executor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E48="Revisor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E48="Auditor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E48="Secretário",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O48" s="46" t="s">
+      <c r="O48" s="32" t="s">
         <v>261</v>
       </c>
       <c r="P48" s="20" t="s">
@@ -7041,15 +7030,15 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="22.8">
+    <row r="49" spans="1:26" ht="24">
       <c r="A49" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>256</v>
@@ -7131,15 +7120,15 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="34.200000000000003">
+    <row r="50" spans="1:26" ht="36">
       <c r="A50" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>258</v>
@@ -7181,7 +7170,7 @@
         <v>73</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q50" s="13">
         <f>IF(OR($A50="",NOT(ISNUMBER($L50)),NOT(ISNUMBER($N50))),"",$L50*$N50)</f>
@@ -7226,10 +7215,10 @@
         <v>267</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>259</v>
@@ -7267,7 +7256,7 @@
         <f>IF($A51="","",IF($M51="","",IF($E51="Executor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E51="Revisor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E51="Auditor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E51="Secretário",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O51" s="46" t="s">
+      <c r="O51" s="32" t="s">
         <v>261</v>
       </c>
       <c r="P51" s="20" t="s">
@@ -7311,15 +7300,15 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="22.8">
+    <row r="52" spans="1:26" ht="24">
       <c r="A52" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>257</v>
@@ -7401,15 +7390,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="34.200000000000003">
+    <row r="53" spans="1:26" ht="36">
       <c r="A53" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>256</v>
@@ -7451,7 +7440,7 @@
         <v>73</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q53" s="13">
         <f t="shared" si="9"/>
@@ -7491,15 +7480,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="31.8" customHeight="1">
+    <row r="54" spans="1:26" ht="31.9" customHeight="1">
       <c r="A54" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>256</v>
@@ -7537,7 +7526,7 @@
         <f>IF($A54="","",IF($M54="","",IF($E54="Executor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E54="Revisor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E54="Auditor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E54="Secretário",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O54" s="46" t="s">
+      <c r="O54" s="32" t="s">
         <v>261</v>
       </c>
       <c r="P54" s="20" t="s">
@@ -7581,15 +7570,15 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="22.8">
+    <row r="55" spans="1:26" ht="24">
       <c r="A55" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>259</v>
@@ -7671,15 +7660,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="34.200000000000003">
+    <row r="56" spans="1:26" ht="36">
       <c r="A56" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>258</v>
@@ -7721,7 +7710,7 @@
         <v>73</v>
       </c>
       <c r="P56" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q56" s="13">
         <f t="shared" si="11"/>
@@ -7761,90 +7750,90 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="34.200000000000003">
-      <c r="A57" s="46" t="s">
+    <row r="57" spans="1:26" ht="36">
+      <c r="A57" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="46"/>
-      <c r="C57" s="46" t="s">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="E57" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="47">
+      <c r="F57" s="33">
         <v>10</v>
       </c>
-      <c r="G57" s="46" t="s">
+      <c r="G57" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="H57" s="48">
+      <c r="H57" s="34">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="I57" s="46" t="s">
+      <c r="I57" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="J57" s="47">
-        <v>0</v>
-      </c>
-      <c r="K57" s="47">
-        <v>0</v>
-      </c>
-      <c r="L57" s="48">
+      <c r="J57" s="33">
+        <v>0</v>
+      </c>
+      <c r="K57" s="33">
+        <v>0</v>
+      </c>
+      <c r="L57" s="34">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="M57" s="46" t="s">
+      <c r="M57" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="N57" s="49">
+      <c r="N57" s="35">
         <f>IF($A57="","",IF($M57="","",IF($E57="Executor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E57="Revisor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E57="Auditor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E57="Secretário",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O57" s="46" t="s">
+      <c r="O57" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="P57" s="46" t="s">
+      <c r="P57" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="Q57" s="48">
+      <c r="Q57" s="34">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="R57" s="50">
+      <c r="R57" s="36">
         <v>46293</v>
       </c>
       <c r="S57" s="23">
         <v>46302.979166666664</v>
       </c>
-      <c r="T57" s="48">
+      <c r="T57" s="34">
         <f t="shared" si="2"/>
         <v>239.49999999994179</v>
       </c>
-      <c r="U57" s="46" t="s">
+      <c r="U57" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="V57" s="49">
+      <c r="V57" s="35">
         <f>IF($A57="","",IF($U57="","",IFERROR(VLOOKUP($U57,'[1]Listas de apoio'!$S$5:$T$10,2,FALSE),"")))</f>
         <v>0</v>
       </c>
-      <c r="W57" s="48">
+      <c r="W57" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X57" s="48">
+      <c r="X57" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="Y57" s="48">
+      <c r="Y57" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="48">
+      <c r="Z57" s="34">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
@@ -7991,6 +7980,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I5:Z5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A4:C4"/>
@@ -8007,29 +8004,21 @@
     <mergeCell ref="I12:Z12"/>
     <mergeCell ref="I13:Z13"/>
     <mergeCell ref="I14:Z14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I5:Z5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="C21:C23">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND($A21&lt;&gt;"",$X21="Aprovada como Ready",OR($B21="",$C21="",$D21="",$E21="",$F21="",$G21="",$H21="",$I21="",$J21="",$N21="",$O21="",$P21="",$Q21="",$R21="",$S21="",$T21="",$U21="",$V21&lt;&gt;"Sim",$Y21="",$Z21=""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C30:C35">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>AND(#REF!&lt;&gt;"",$X26="Aprovada como Ready",OR($B27="",$C30="",$D27="",$E27="",$F27="",$G27="",$H27="",$I27="",$J27="",$N27="",$O26="",$P26="",$Q26="",$R26="",$S26="",$T26="",$U26="",$V26&lt;&gt;"Sim",$Y26="",$Z26=""))</formula>
+  <conditionalFormatting sqref="C27:C29">
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>AND(#REF!&lt;&gt;"",$X24="Aprovada como Ready",OR($B24="",$C27="",$D24="",$E24="",$F24="",$G24="",$H24="",$I24="",$J24="",$N24="",$O24="",$P24="",$Q24="",$R24="",$S24="",$T24="",$U24="",$V24&lt;&gt;"Sim",$Y24="",$Z24=""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C29">
-    <cfRule type="expression" dxfId="4" priority="7">
-      <formula>AND(#REF!&lt;&gt;"",$X24="Aprovada como Ready",OR($B24="",$C27="",$D24="",$E24="",$F24="",$G24="",$H24="",$I24="",$J24="",$N24="",$O24="",$P24="",$Q24="",$R24="",$S24="",$T24="",$U24="",$V24&lt;&gt;"Sim",$Y24="",$Z24=""))</formula>
+  <conditionalFormatting sqref="C30:C35">
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>AND(#REF!&lt;&gt;"",$X26="Aprovada como Ready",OR($B27="",$C30="",$D27="",$E27="",$F27="",$G27="",$H27="",$I27="",$J27="",$N27="",$O26="",$P26="",$Q26="",$R26="",$S26="",$T26="",$U26="",$V26&lt;&gt;"Sim",$Y26="",$Z26=""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
@@ -8072,7 +8061,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -8081,30 +8070,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="37" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="40" t="s">
         <v>89</v>
       </c>
     </row>
@@ -8637,8 +8626,8 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:C33">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Rever"/>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Rever"/>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="OK"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8650,7 +8639,7 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8658,30 +8647,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="37" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="40" t="s">
         <v>137</v>
       </c>
     </row>
@@ -9126,7 +9115,7 @@
     <tabColor rgb="FFFFD966"/>
   </sheetPr>
   <dimension ref="A1:AG220"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -9149,192 +9138,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="26.1" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="V1" s="34" t="s">
+      <c r="V1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="34" t="s">
+      <c r="W1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="X1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="Y1" s="34" t="s">
+      <c r="Y1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="Z1" s="34" t="s">
+      <c r="Z1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AA1" s="34" t="s">
+      <c r="AA1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AB1" s="34" t="s">
+      <c r="AB1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AC1" s="34" t="s">
+      <c r="AC1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AD1" s="34" t="s">
+      <c r="AD1" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="AE1" s="34" t="s">
+      <c r="AE1" s="37" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="33.9" customHeight="1">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:33" ht="33.950000000000003" customHeight="1">
+      <c r="A2" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="Q2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="R2" s="36" t="s">
+      <c r="R2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="S2" s="36" t="s">
+      <c r="S2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="T2" s="36" t="s">
+      <c r="T2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="U2" s="36" t="s">
+      <c r="U2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="W2" s="36" t="s">
+      <c r="W2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="X2" s="36" t="s">
+      <c r="X2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="Y2" s="36" t="s">
+      <c r="Y2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="Z2" s="36" t="s">
+      <c r="Z2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="AA2" s="36" t="s">
+      <c r="AA2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="AB2" s="36" t="s">
+      <c r="AB2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AC2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="AD2" s="36" t="s">
+      <c r="AD2" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="AE2" s="37" t="s">
+      <c r="AE2" s="40" t="s">
         <v>198</v>
       </c>
     </row>
@@ -9371,7 +9360,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:33" ht="20.399999999999999">
+    <row r="4" spans="1:33" ht="33.75">
       <c r="A4" s="2" t="s">
         <v>199</v>
       </c>
@@ -9552,7 +9541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" ht="24">
       <c r="A6" s="3" t="s">
         <v>257</v>
       </c>
@@ -9648,7 +9637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="22.8">
+    <row r="7" spans="1:33" ht="24">
       <c r="A7" s="3" t="s">
         <v>259</v>
       </c>
@@ -9908,7 +9897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="22.8">
+    <row r="10" spans="1:33" ht="24">
       <c r="A10" s="19"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -24109,9 +24098,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81e1889baf096e0f1fabc7e628f510b3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b8b816b6954550eb9ea5c593f5cc868" ns2:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="59ec22bb-74c1-4c3c-af96-122e757b18d2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32f33a6e-f018-4796-a6d6-b8c30f0661e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="9" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="67106ac685bde41cc0caab8279921af5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" xmlns:ns3="59ec22bb-74c1-4c3c-af96-122e757b18d2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a225e97788944c998cfd0bee463245c" ns2:_="" ns3:_="">
     <xsd:import namespace="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
+    <xsd:import namespace="59ec22bb-74c1-4c3c-af96-122e757b18d2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -24121,6 +24122,11 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -24146,6 +24152,43 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1374c586-51ca-419d-b13a-551147e70874" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="59ec22bb-74c1-4c3c-af96-122e757b18d2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{281605ea-d3cc-4310-8c97-aa0e64c9f496}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="59ec22bb-74c1-4c3c-af96-122e757b18d2">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -24156,8 +24199,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -24246,12 +24289,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E746F47-194E-4081-A62E-6ADB0FFE3951}">
   <ds:schemaRefs>
@@ -24261,24 +24298,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C66B1CD-6A0F-4114-9FEA-12582C609DBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D1F82A-C528-4FA7-A067-BA278DE3DDB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -24292,4 +24311,8 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CE3528-0E42-4F7A-B8FF-FA9D59FC0D5D}"/>
 </file>
--- a/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-s02-mapa-pontuacao-individual-v01.xlsx
+++ b/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-s02-mapa-pontuacao-individual-v01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{9CCF419F-787D-4318-8B09-C392A2B7CFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01E38B2-6A29-416C-9362-B0E343E29533}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCF419F-787D-4318-8B09-C392A2B7CFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa de Pontuação Individual" sheetId="1" r:id="rId1"/>
@@ -887,6 +887,9 @@
     <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.xlsx</t>
   </si>
   <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.pdf</t>
+  </si>
+  <si>
     <t>I011</t>
   </si>
   <si>
@@ -981,9 +984,6 @@
   </si>
   <si>
     <t>André Filipe Moreira Mesquita; Gonçalo Dinis Magalhães Teixeira; Gonçalo Magalhães Ribeiro</t>
-  </si>
-  <si>
-    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-20261007-sprint-backlog-v01.pdf</t>
   </si>
 </sst>
 </file>
@@ -1375,6 +1375,48 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1393,53 +1435,59 @@
     <xf numFmtId="164" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="34">
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4C6E7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4C6E7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4C6E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4C6E7"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFB4C6E7"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFB4C6E7"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4C6E7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4C6E7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4C6E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4C6E7"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFB4C6E7"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFB4C6E7"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1491,25 +1539,15 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB4C6E7"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFB4C6E7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB4C6E7"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFB4C6E7"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFB4C6E7"/>
-        </horizontal>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1563,33 +1601,7 @@
         <left style="thin">
           <color rgb="FFB4C6E7"/>
         </left>
-        <right style="thin">
-          <color rgb="FFB4C6E7"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFB4C6E7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB4C6E7"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFB4C6E7"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFB4C6E7"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB4C6E7"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFB4C6E7"/>
-        </right>
+        <right/>
         <top style="thin">
           <color rgb="FFB4C6E7"/>
         </top>
@@ -1766,7 +1778,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2289,50 +2300,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DetalhePontuacaoTable" displayName="DetalhePontuacaoTable" ref="A17:Z57" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DetalhePontuacaoTable" displayName="DetalhePontuacaoTable" ref="A17:Z57" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Sprint" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Issue" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tarefa" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aluno" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Papel" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Orçamento da tarefa" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Origem da parcela" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="PMI" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Referência da transferência" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="PC" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="PR" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="PMR" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Sprint" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Issue" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tarefa" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aluno" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Papel" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Orçamento da tarefa" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Origem da parcela" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="PMI" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Referência da transferência" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="PC" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="PR" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="PMR" dataDxfId="21">
       <calculatedColumnFormula>IF($A18="","",$H18-$J18+$K18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Categoria de qualidade aprovada" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Q" dataDxfId="17">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Categoria de qualidade aprovada" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Q" dataDxfId="1">
       <calculatedColumnFormula>IF($A18="","",IF($M18="","",IF($E18="Executor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E18="Revisor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E18="Auditor",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E18="Secretário",IFERROR(VLOOKUP($M18,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Fundamento e evidência" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Classificação atribuída por" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="PQ" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Fundamento e evidência" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Classificação atribuída por" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="PQ" dataDxfId="18">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($L18)),NOT(ISNUMBER($N18))),"",$L18*$N18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Prazo aplicável" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Data e hora de conclusão" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Atraso imputável em horas" dataDxfId="11">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Prazo aplicável" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Data e hora de conclusão" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Atraso imputável em horas" dataDxfId="15">
       <calculatedColumnFormula>IF(OR($A18="",$R18="",$S18=""),"",MAX(0,($S18-$R18)*24))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Penalização por atraso" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="A" dataDxfId="9">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Penalização por atraso" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="A" dataDxfId="0">
       <calculatedColumnFormula>IF($A18="","",IF($U18="","",IFERROR(VLOOKUP($U18,'[1]Listas de apoio'!$S$5:$T$10,2,FALSE),"")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="Perda por qualidade" dataDxfId="8">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="Perda por qualidade" dataDxfId="13">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($L18)),NOT(ISNUMBER($Q18))),"",$L18-$Q18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="PEO não arredondado" dataDxfId="7">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="PEO não arredondado" dataDxfId="12">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($Q18)),NOT(ISNUMBER($V18))),"",$Q18*(1-$V18))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="Perda por atraso" dataDxfId="6">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="Perda por atraso" dataDxfId="11">
       <calculatedColumnFormula>IF(OR($A18="",NOT(ISNUMBER($Q18)),NOT(ISNUMBER($X18))),"",$Q18-$X18)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0100-00001A000000}" name="PEO" dataDxfId="5">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0100-00001A000000}" name="PEO" dataDxfId="10">
       <calculatedColumnFormula>IF(NOT(ISNUMBER($X18)),"",ROUND($X18,2))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2539,66 +2550,66 @@
     <tabColor rgb="FF17365D"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.375" customWidth="1"/>
-    <col min="4" max="4" width="22.625" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.3984375" customWidth="1"/>
+    <col min="4" max="4" width="22.59765625" customWidth="1"/>
+    <col min="5" max="5" width="22.3984375" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37" t="s">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.1" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="37" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2612,29 +2623,29 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A4" s="48" t="s">
+    <row r="4" spans="1:9" ht="21.9" customHeight="1">
+      <c r="A4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="33" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2667,7 +2678,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="29"/>
     </row>
-    <row r="7" spans="1:9" ht="25.15" customHeight="1">
+    <row r="7" spans="1:9" ht="25.2" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
@@ -2696,7 +2707,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="28.15" customHeight="1">
+    <row r="9" spans="1:9" ht="28.2" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
@@ -2711,7 +2722,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="26.45" customHeight="1">
+    <row r="10" spans="1:9" ht="26.4" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
@@ -2736,33 +2747,33 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A12" s="48" t="s">
+    <row r="12" spans="1:9" ht="21.9" customHeight="1">
+      <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="49" t="s">
+      <c r="G12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="33.950000000000003" customHeight="1">
+    <row r="13" spans="1:9" ht="33.9" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2822,7 +2833,7 @@
         <v>19.522546419098148</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="24">
+    <row r="15" spans="1:9">
       <c r="A15" s="7" t="str">
         <f>'Listas de apoio'!A6</f>
         <v>Gonçalo Dinis Magalhães Teixeira</v>
@@ -2961,29 +2972,29 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A20" s="48" t="s">
+    <row r="20" spans="1:8" ht="21.9" customHeight="1">
+      <c r="A20" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="49" t="s">
+      <c r="E20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="49" t="s">
+      <c r="F20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="49" t="s">
+      <c r="G20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="33" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3037,7 +3048,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="24">
+    <row r="24" spans="1:8" ht="22.8">
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
@@ -3065,22 +3076,22 @@
       <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="33" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="1"/>
@@ -3363,7 +3374,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" ht="24">
+    <row r="37" spans="1:8">
       <c r="A37" s="10" t="s">
         <v>33</v>
       </c>
@@ -3445,11 +3456,11 @@
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
   <dimension ref="A1:AF62"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="32.75" customWidth="1"/>
-    <col min="4" max="4" width="26.125" customWidth="1"/>
+    <col min="3" max="3" width="32.796875" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
@@ -3473,162 +3484,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="26.1" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="X1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Z1" s="34" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="44.1" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="S2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="T2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="U2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="39" t="s">
+      <c r="W2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="X2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="Z2" s="37" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3660,14 +3671,14 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:32" ht="21.95" customHeight="1">
-      <c r="A4" s="41" t="s">
+    <row r="4" spans="1:32" ht="21.9" customHeight="1">
+      <c r="A4" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="1"/>
@@ -3694,39 +3705,39 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:32" s="11" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:32" s="11" customFormat="1" ht="33.9" customHeight="1">
       <c r="A5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45" t="s">
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="45"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="39"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="39"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3738,35 +3749,35 @@
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="46" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="38"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -3778,35 +3789,35 @@
       <c r="A7" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -3816,31 +3827,31 @@
     </row>
     <row r="8" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="47"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="47"/>
-      <c r="X8" s="47"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -3850,31 +3861,31 @@
     </row>
     <row r="9" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
-      <c r="X9" s="47"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -3884,31 +3895,31 @@
     </row>
     <row r="10" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -3918,31 +3929,31 @@
     </row>
     <row r="11" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
@@ -3952,31 +3963,31 @@
     </row>
     <row r="12" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -3986,31 +3997,31 @@
     </row>
     <row r="13" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A13" s="3"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -4020,31 +4031,31 @@
     </row>
     <row r="14" spans="1:32" s="11" customFormat="1" ht="31.5" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -4080,83 +4091,83 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:32" ht="21.95" customHeight="1">
-      <c r="A16" s="44" t="s">
+    <row r="16" spans="1:32" ht="21.9" customHeight="1">
+      <c r="A16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="F16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="44" t="s">
+      <c r="I16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="44" t="s">
+      <c r="J16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="44" t="s">
+      <c r="K16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="44" t="s">
+      <c r="L16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="M16" s="44" t="s">
+      <c r="M16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="44" t="s">
+      <c r="N16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="44" t="s">
+      <c r="O16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="P16" s="44" t="s">
+      <c r="P16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="Q16" s="44" t="s">
+      <c r="Q16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="R16" s="44" t="s">
+      <c r="R16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="S16" s="44" t="s">
+      <c r="S16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="T16" s="44" t="s">
+      <c r="T16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="U16" s="44" t="s">
+      <c r="U16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="44" t="s">
+      <c r="V16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="W16" s="44" t="s">
+      <c r="W16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="X16" s="44" t="s">
+      <c r="X16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="Y16" s="44" t="s">
+      <c r="Y16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="Z16" s="44" t="s">
+      <c r="Z16" s="43" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4245,10 +4256,10 @@
         <v>267</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>259</v>
@@ -4335,10 +4346,10 @@
         <v>267</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>258</v>
@@ -4425,10 +4436,10 @@
         <v>267</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>257</v>
@@ -4515,10 +4526,10 @@
         <v>267</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>257</v>
@@ -4605,10 +4616,10 @@
         <v>267</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>259</v>
@@ -4695,10 +4706,10 @@
         <v>267</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>256</v>
@@ -4740,7 +4751,7 @@
         <v>73</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q23" s="13">
         <f t="shared" si="1"/>
@@ -4785,10 +4796,10 @@
         <v>267</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>256</v>
@@ -4875,10 +4886,10 @@
         <v>267</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>257</v>
@@ -4965,10 +4976,10 @@
         <v>267</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>259</v>
@@ -5010,7 +5021,7 @@
         <v>73</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q26" s="13">
         <f t="shared" si="1"/>
@@ -5055,10 +5066,10 @@
         <v>267</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>257</v>
@@ -5145,10 +5156,10 @@
         <v>267</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>259</v>
@@ -5235,10 +5246,10 @@
         <v>267</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>258</v>
@@ -5280,7 +5291,7 @@
         <v>73</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q29" s="13">
         <f t="shared" si="1"/>
@@ -5325,10 +5336,10 @@
         <v>267</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>258</v>
@@ -5415,10 +5426,10 @@
         <v>267</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>256</v>
@@ -5505,10 +5516,10 @@
         <v>267</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>259</v>
@@ -5550,7 +5561,7 @@
         <v>73</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q32" s="13">
         <f t="shared" si="1"/>
@@ -5595,10 +5606,10 @@
         <v>267</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>288</v>
+        <v>276</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>289</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>259</v>
@@ -5685,10 +5696,10 @@
         <v>267</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>288</v>
+        <v>276</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>289</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>257</v>
@@ -5775,13 +5786,13 @@
         <v>267</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>288</v>
+        <v>276</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>289</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>71</v>
@@ -5820,7 +5831,7 @@
         <v>73</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q35" s="13">
         <f t="shared" si="1"/>
@@ -5865,10 +5876,10 @@
         <v>267</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>257</v>
@@ -5955,10 +5966,10 @@
         <v>267</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>259</v>
@@ -6045,10 +6056,10 @@
         <v>267</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>258</v>
@@ -6090,7 +6101,7 @@
         <v>73</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q38" s="13">
         <f t="shared" si="1"/>
@@ -6135,10 +6146,10 @@
         <v>267</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>256</v>
@@ -6225,10 +6236,10 @@
         <v>267</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>258</v>
@@ -6315,10 +6326,10 @@
         <v>267</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>259</v>
@@ -6360,7 +6371,7 @@
         <v>73</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q41" s="13">
         <f t="shared" si="1"/>
@@ -6405,10 +6416,10 @@
         <v>267</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>257</v>
@@ -6495,10 +6506,10 @@
         <v>267</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>259</v>
@@ -6585,10 +6596,10 @@
         <v>267</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>256</v>
@@ -6630,7 +6641,7 @@
         <v>73</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q44" s="13">
         <f t="shared" si="1"/>
@@ -6675,10 +6686,10 @@
         <v>267</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>256</v>
@@ -6716,7 +6727,7 @@
         <f>IF($A45="","",IF($M45="","",IF($E45="Executor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E45="Revisor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E45="Auditor",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E45="Secretário",IFERROR(VLOOKUP($M45,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O45" s="32" t="s">
+      <c r="O45" s="46" t="s">
         <v>261</v>
       </c>
       <c r="P45" s="20" t="s">
@@ -6765,10 +6776,10 @@
         <v>267</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>258</v>
@@ -6855,10 +6866,10 @@
         <v>267</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>257</v>
@@ -6945,10 +6956,10 @@
         <v>267</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>257</v>
@@ -6986,7 +6997,7 @@
         <f>IF($A48="","",IF($M48="","",IF($E48="Executor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E48="Revisor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E48="Auditor",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E48="Secretário",IFERROR(VLOOKUP($M48,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O48" s="32" t="s">
+      <c r="O48" s="46" t="s">
         <v>261</v>
       </c>
       <c r="P48" s="20" t="s">
@@ -7030,15 +7041,15 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="24">
+    <row r="49" spans="1:26" ht="22.8">
       <c r="A49" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>256</v>
@@ -7120,15 +7131,15 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="36">
+    <row r="50" spans="1:26" ht="34.200000000000003">
       <c r="A50" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>258</v>
@@ -7170,7 +7181,7 @@
         <v>73</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q50" s="13">
         <f>IF(OR($A50="",NOT(ISNUMBER($L50)),NOT(ISNUMBER($N50))),"",$L50*$N50)</f>
@@ -7215,10 +7226,10 @@
         <v>267</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>259</v>
@@ -7256,7 +7267,7 @@
         <f>IF($A51="","",IF($M51="","",IF($E51="Executor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E51="Revisor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E51="Auditor",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E51="Secretário",IFERROR(VLOOKUP($M51,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O51" s="32" t="s">
+      <c r="O51" s="46" t="s">
         <v>261</v>
       </c>
       <c r="P51" s="20" t="s">
@@ -7300,15 +7311,15 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="24">
+    <row r="52" spans="1:26" ht="22.8">
       <c r="A52" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>257</v>
@@ -7390,15 +7401,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="36">
+    <row r="53" spans="1:26" ht="34.200000000000003">
       <c r="A53" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>256</v>
@@ -7440,7 +7451,7 @@
         <v>73</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q53" s="13">
         <f t="shared" si="9"/>
@@ -7480,15 +7491,15 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="31.9" customHeight="1">
+    <row r="54" spans="1:26" ht="31.8" customHeight="1">
       <c r="A54" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>256</v>
@@ -7526,7 +7537,7 @@
         <f>IF($A54="","",IF($M54="","",IF($E54="Executor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E54="Revisor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E54="Auditor",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E54="Secretário",IFERROR(VLOOKUP($M54,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O54" s="32" t="s">
+      <c r="O54" s="46" t="s">
         <v>261</v>
       </c>
       <c r="P54" s="20" t="s">
@@ -7570,15 +7581,15 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="24">
+    <row r="55" spans="1:26" ht="22.8">
       <c r="A55" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>259</v>
@@ -7660,15 +7671,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="36">
+    <row r="56" spans="1:26" ht="34.200000000000003">
       <c r="A56" s="20" t="s">
         <v>267</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>258</v>
@@ -7710,7 +7721,7 @@
         <v>73</v>
       </c>
       <c r="P56" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q56" s="13">
         <f t="shared" si="11"/>
@@ -7750,90 +7761,90 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="36">
-      <c r="A57" s="32" t="s">
+    <row r="57" spans="1:26" ht="34.200000000000003">
+      <c r="A57" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32" t="s">
+      <c r="B57" s="46"/>
+      <c r="C57" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="46" t="s">
         <v>259</v>
       </c>
-      <c r="E57" s="32" t="s">
+      <c r="E57" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="47">
         <v>10</v>
       </c>
-      <c r="G57" s="32" t="s">
+      <c r="G57" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="48">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="I57" s="32" t="s">
+      <c r="I57" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="J57" s="33">
-        <v>0</v>
-      </c>
-      <c r="K57" s="33">
-        <v>0</v>
-      </c>
-      <c r="L57" s="34">
+      <c r="J57" s="47">
+        <v>0</v>
+      </c>
+      <c r="K57" s="47">
+        <v>0</v>
+      </c>
+      <c r="L57" s="48">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="M57" s="32" t="s">
+      <c r="M57" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="N57" s="35">
+      <c r="N57" s="49">
         <f>IF($A57="","",IF($M57="","",IF($E57="Executor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$G$5:$H$9,2,FALSE),""),IF($E57="Revisor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$J$5:$K$8,2,FALSE),""),IF($E57="Auditor",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$M$5:$N$7,2,FALSE),""),IF($E57="Secretário",IFERROR(VLOOKUP($M57,'[1]Listas de apoio'!$P$5:$Q$7,2,FALSE),""),""))))))</f>
         <v>1</v>
       </c>
-      <c r="O57" s="32" t="s">
+      <c r="O57" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="P57" s="32" t="s">
+      <c r="P57" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="Q57" s="34">
+      <c r="Q57" s="48">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="R57" s="36">
+      <c r="R57" s="50">
         <v>46293</v>
       </c>
       <c r="S57" s="23">
         <v>46302.979166666664</v>
       </c>
-      <c r="T57" s="34">
+      <c r="T57" s="48">
         <f t="shared" si="2"/>
         <v>239.49999999994179</v>
       </c>
-      <c r="U57" s="32" t="s">
+      <c r="U57" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="V57" s="35">
+      <c r="V57" s="49">
         <f>IF($A57="","",IF($U57="","",IFERROR(VLOOKUP($U57,'[1]Listas de apoio'!$S$5:$T$10,2,FALSE),"")))</f>
         <v>0</v>
       </c>
-      <c r="W57" s="34">
+      <c r="W57" s="48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X57" s="34">
+      <c r="X57" s="48">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="Y57" s="34">
+      <c r="Y57" s="48">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="34">
+      <c r="Z57" s="48">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
@@ -7980,14 +7991,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I5:Z5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A4:C4"/>
@@ -8004,21 +8007,29 @@
     <mergeCell ref="I12:Z12"/>
     <mergeCell ref="I13:Z13"/>
     <mergeCell ref="I14:Z14"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I5:Z5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="C21:C23">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AND($A21&lt;&gt;"",$X21="Aprovada como Ready",OR($B21="",$C21="",$D21="",$E21="",$F21="",$G21="",$H21="",$I21="",$J21="",$N21="",$O21="",$P21="",$Q21="",$R21="",$S21="",$T21="",$U21="",$V21&lt;&gt;"Sim",$Y21="",$Z21=""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:C29">
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>AND(#REF!&lt;&gt;"",$X24="Aprovada como Ready",OR($B24="",$C27="",$D24="",$E24="",$F24="",$G24="",$H24="",$I24="",$J24="",$N24="",$O24="",$P24="",$Q24="",$R24="",$S24="",$T24="",$U24="",$V24&lt;&gt;"Sim",$Y24="",$Z24=""))</formula>
+  <conditionalFormatting sqref="C30:C35">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AND(#REF!&lt;&gt;"",$X26="Aprovada como Ready",OR($B27="",$C30="",$D27="",$E27="",$F27="",$G27="",$H27="",$I27="",$J27="",$N27="",$O26="",$P26="",$Q26="",$R26="",$S26="",$T26="",$U26="",$V26&lt;&gt;"Sim",$Y26="",$Z26=""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C30:C35">
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>AND(#REF!&lt;&gt;"",$X26="Aprovada como Ready",OR($B27="",$C30="",$D27="",$E27="",$F27="",$G27="",$H27="",$I27="",$J27="",$N27="",$O26="",$P26="",$Q26="",$R26="",$S26="",$T26="",$U26="",$V26&lt;&gt;"Sim",$Y26="",$Z26=""))</formula>
+  <conditionalFormatting sqref="C27:C29">
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>AND(#REF!&lt;&gt;"",$X24="Aprovada como Ready",OR($B24="",$C27="",$D24="",$E24="",$F24="",$G24="",$H24="",$I24="",$J24="",$N24="",$O24="",$P24="",$Q24="",$R24="",$S24="",$T24="",$U24="",$V24&lt;&gt;"Sim",$Y24="",$Z24=""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
@@ -8061,7 +8072,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -8070,30 +8081,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="37" t="s">
         <v>89</v>
       </c>
     </row>
@@ -8626,8 +8637,8 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:C33">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Rever"/>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Rever"/>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="OK"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8639,7 +8650,7 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8647,30 +8658,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="38.1" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="37" t="s">
         <v>137</v>
       </c>
     </row>
@@ -9115,7 +9126,7 @@
     <tabColor rgb="FFFFD966"/>
   </sheetPr>
   <dimension ref="A1:AG220"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -9138,192 +9149,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="26.1" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="X1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Z1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="AA1" s="37" t="s">
+      <c r="AA1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="AB1" s="37" t="s">
+      <c r="AB1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="AC1" s="37" t="s">
+      <c r="AC1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="AD1" s="37" t="s">
+      <c r="AD1" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AE1" s="34" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="38" t="s">
+    <row r="2" spans="1:33" ht="33.9" customHeight="1">
+      <c r="A2" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="S2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="T2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="U2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="W2" s="39" t="s">
+      <c r="W2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="X2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="Z2" s="39" t="s">
+      <c r="Z2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="AA2" s="39" t="s">
+      <c r="AA2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="AB2" s="39" t="s">
+      <c r="AB2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="AC2" s="39" t="s">
+      <c r="AC2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="AD2" s="39" t="s">
+      <c r="AD2" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="AE2" s="40" t="s">
+      <c r="AE2" s="37" t="s">
         <v>198</v>
       </c>
     </row>
@@ -9360,7 +9371,7 @@
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
     </row>
-    <row r="4" spans="1:33" ht="33.75">
+    <row r="4" spans="1:33" ht="20.399999999999999">
       <c r="A4" s="2" t="s">
         <v>199</v>
       </c>
@@ -9541,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="24">
+    <row r="6" spans="1:33">
       <c r="A6" s="3" t="s">
         <v>257</v>
       </c>
@@ -9637,7 +9648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="24">
+    <row r="7" spans="1:33" ht="22.8">
       <c r="A7" s="3" t="s">
         <v>259</v>
       </c>
@@ -9897,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="24">
+    <row r="10" spans="1:33" ht="22.8">
       <c r="A10" s="19"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -24098,21 +24109,9 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="59ec22bb-74c1-4c3c-af96-122e757b18d2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32f33a6e-f018-4796-a6d6-b8c30f0661e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="9" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="67106ac685bde41cc0caab8279921af5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" xmlns:ns3="59ec22bb-74c1-4c3c-af96-122e757b18d2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a225e97788944c998cfd0bee463245c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81e1889baf096e0f1fabc7e628f510b3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b8b816b6954550eb9ea5c593f5cc868" ns2:_="">
     <xsd:import namespace="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
-    <xsd:import namespace="59ec22bb-74c1-4c3c-af96-122e757b18d2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -24122,11 +24121,6 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -24152,43 +24146,6 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1374c586-51ca-419d-b13a-551147e70874" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="59ec22bb-74c1-4c3c-af96-122e757b18d2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{281605ea-d3cc-4310-8c97-aa0e64c9f496}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="59ec22bb-74c1-4c3c-af96-122e757b18d2">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -24199,8 +24156,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -24289,6 +24246,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E746F47-194E-4081-A62E-6ADB0FFE3951}">
   <ds:schemaRefs>
@@ -24298,6 +24261,24 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C66B1CD-6A0F-4114-9FEA-12582C609DBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D1F82A-C528-4FA7-A067-BA278DE3DDB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -24311,8 +24292,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CE3528-0E42-4F7A-B8FF-FA9D59FC0D5D}"/>
 </file>